--- a/EstablecimientoSalud/excels/APURIMAC-ABANCAY-ABANCAY.xlsx
+++ b/EstablecimientoSalud/excels/APURIMAC-ABANCAY-ABANCAY.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,12 +493,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>34318</t>
+          <t>11216</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>30101</t>
+          <t>30104</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -513,32 +513,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ABANCAY</t>
+          <t>CURAHUASI</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-13.6380026</t>
+          <t>-13.53678672</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-72.87867301</t>
+          <t>-72.69819253</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>CENTRO MEDICO PSICOSOMATICO SEAOR DE LOS MILAGROS</t>
+          <t>CENTRO DE ATENCION PRIMARIA I CURAHUASI</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>AVENIDA MARIAO NUMERO 161 PISO 1 DISTRITO ABANCAY PROVINCIA ABANCAY DEPARTAMENTO APURIMAC</t>
+          <t>JR. ABANCAY Nº 331 DISTRITO CURAHUASI PROVINCIA ABANCAY DEPARTAMENTO APURIMAC</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -555,12 +555,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>30680</t>
+          <t>34572</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>30101</t>
+          <t>30104</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -575,32 +575,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ABANCAY</t>
+          <t>CURAHUASI</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-13.63394832</t>
+          <t>-13.537735</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-72.8884824</t>
+          <t>-72.7001397</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CONSULTORIO DENTAL SEAOR DE SOCCLLACCASA</t>
+          <t>CENTRO DE ATENCION PRIMARIA II CURAHUASI</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>COLOMBIA NUMERO 112 PISO 2 URBANIZACION LAS AMERICAS DISTRITO ABANCAY PROVINCIA ABANCAY DEPARTAMENTO APURIMAC</t>
+          <t>CALLE LOS GERANIOS NUMERO S/N PISO 1 DISTRITO CURAHUASI PROVINCIA ABANCAY DEPARTAMENTO APURIMAC</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>I-1</t>
+          <t>I-3</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -617,7 +617,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>31450</t>
+          <t>8036</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -642,22 +642,22 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-13.62992625</t>
+          <t>-13.63107169</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-72.88602818</t>
+          <t>-72.88813747</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CENTRO MEDICO SAN MIGUEL</t>
+          <t>POLICLINICO POLICIAL ABANCAY</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AVENIDA VICTOR RAUL HAYA DE LA TORRE MANZANA F LOTE 15 DISTRITO ABANCAY PROVINCIA ABANCAY DEPARTAMENTO APURIMAC</t>
+          <t>JR. SANIDAD S/N BARRIO POLICIAL VILLA AMPAY NUMERO S/N DISTRITO ABANCAY PROVINCIA ABANCAY DEPARTAMENTO APURIMAC</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,7 +679,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>34107</t>
+          <t>25996</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -704,27 +704,27 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-13.6396564</t>
+          <t>-13.63485776</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-72.8926263</t>
+          <t>-72.8796795</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>CONSULTORIO ODONTOLOGICO MOLERO</t>
+          <t>CENTRO DE SALUD MENTAL COMUNITARIO "QHALI KAY"</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SALVADOR NUMERO 200 PISO 2 URBANIZACION LAS AMERICAS DISTRITO ABANCAY PROVINCIA ABANCAY DEPARTAMENTO APURIMAC</t>
+          <t>PASAJE SOUSA 118 1 COSTADO IZQUIERDO DEL HOTEL DE TURISTAS DE ABANCAY ABANCAY ABANCAY APURIMAC</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>I-1</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -741,12 +741,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>34456</t>
+          <t>26572</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>30101</t>
+          <t>30104</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,32 +761,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ABANCAY</t>
+          <t>CURAHUASI</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-13.6415639</t>
+          <t>-13.53785701</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-72.8933335</t>
+          <t>-72.69575002</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Consultorio Odontologico Gomedi</t>
+          <t>CENTRO DE SALUD MENTAL COMUNITARIO "ALLIN KAWSAY"</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>AVENIDA Aviacion MANZANA w LOTE 04 DISTRITO ABANCAY PROVINCIA ABANCAY DEPARTAMENTO APURIMAC</t>
+          <t>AVENIDA LOS ROSALES NUMERO S/N PISO 1 DISTRITO CURAHUASI PROVINCIA ABANCAY DEPARTAMENTO APURIMAC</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>I-1</t>
+          <t>I-3</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -803,7 +803,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>13488</t>
+          <t>2661</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -828,27 +828,27 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-13.6369239</t>
+          <t>-13.62778285</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-72.8803745</t>
+          <t>-72.85941691</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>CENTRO DIAGNOSTICO LOS ANGELES</t>
+          <t>MARCAHUASI</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>JR LIMA Nº 609 JR LIMA Nº 609 ABANCAY ABANCAY APURIMAC</t>
+          <t>OTROS SECTOR MARCAHUASI S/N NUMERO S/N DISTRITO ABANCAY PROVINCIA ABANCAY DEPARTAMENTO APURIMAC</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -865,7 +865,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>31021</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,27 +890,27 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-13.63815563</t>
+          <t>-13.64550167</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-72.88003383</t>
+          <t>-72.90004</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>"GALENUÂ´S MEDICAL GROUP CLINICA "</t>
+          <t>TABLADA ALTA</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>AVENIDA CENTENARIO 120 ABANCAY ABANCAY APURIMAC</t>
+          <t>OTROS TABLA ALTA S/N NUMERO S/N DISTRITO ABANCAY PROVINCIA ABANCAY DEPARTAMENTO APURIMAC</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>I-4</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -927,7 +927,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>24809</t>
+          <t>2662</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -952,27 +952,27 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-13.6391954</t>
+          <t>-13.6801621</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-72.8929</t>
+          <t>-72.86911017</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>POLICLINICO AMERICANA MEDIC ABANCAY S.R.L.</t>
+          <t>QUISAPATA</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>PROLONGACION CUSCO NUMERO 1103 DISTRITO ABANCAY PROVINCIA ABANCAY DEPARTAMENTO APURIMAC</t>
+          <t>OTROS SECTOR QUISAPATA S/N S/N SECTOR QUISAPATA S/N ABANCAY ABANCAY APURIMAC</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -989,7 +989,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>33176</t>
+          <t>7689</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1014,27 +1014,27 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-13.63623642</t>
+          <t>-13.61922015</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-72.88258362</t>
+          <t>-72.91554856</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>POLICLINICO LOS ANGELES</t>
+          <t>HUAYLLABAMBA</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>LIMA NUMERO 848 DISTRITO ABANCAY PROVINCIA ABANCAY DEPARTAMENTO APURIMAC</t>
+          <t>OTROS ACTUALIZAR ACTUALIZAR ABANCAY ABANCAY APURIMAC</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1051,7 +1051,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>34121</t>
+          <t>8828</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1076,27 +1076,27 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-13.64147595</t>
+          <t>-13.63810714</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-72.8892787</t>
+          <t>-72.89122328</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>CONSULTORIO  DE OBSTETRICIA DE LA MUJER "ROSARIO"</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>URBANIZACION AV. AYACUCHO /MOLLE 1 CUADRA NUMERO S/N PISO 1 LOTE 1 URBANIZACION LAS PALMERAS DISTRITO ABANCAY PROVINCIA ABANCAY DEPARTAMENTO APURIMAC</t>
+          <t>OTROS URBANIZACION SAN MARTIN URBANIZACION SAN MARTIN ABANCAY ABANCAY APURIMAC</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>I-1</t>
+          <t>I-3</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1113,12 +1113,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>11216</t>
+          <t>2659</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>30104</t>
+          <t>30101</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1133,32 +1133,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CURAHUASI</t>
+          <t>ABANCAY</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-13.53678672</t>
+          <t>-13.62899</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-72.69819253</t>
+          <t>-72.88469667</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>CENTRO DE ATENCION PRIMARIA I CURAHUASI</t>
+          <t>DR. CARLOS ALFREDO AYESTAS LA TORRE</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>JR. ABANCAY Nº 331 DISTRITO CURAHUASI PROVINCIA ABANCAY DEPARTAMENTO APURIMAC</t>
+          <t>AVENIDA AV. CENTENARIO S/N VILLA AMPAY S/N AV. CENTENARIO S/N VILLA AMPAY ABANCAY ABANCAY APURIMAC</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>I-2</t>
+          <t>I-4</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1175,12 +1175,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>34572</t>
+          <t>2664</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>30104</t>
+          <t>30101</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1195,27 +1195,27 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CURAHUASI</t>
+          <t>ABANCAY</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-13.537735</t>
+          <t>-13.63543084</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-72.7001397</t>
+          <t>-72.89321087</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>CENTRO DE ATENCION PRIMARIA II CURAHUASI</t>
+          <t>BELLAVISTA</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>CALLE LOS GERANIOS NUMERO S/N PISO 1 DISTRITO CURAHUASI PROVINCIA ABANCAY DEPARTAMENTO APURIMAC</t>
+          <t>JIRON LOS SAUCES S/N BELLAVISTA ALTA S/N JIRON LOS SAUCES S/N BELLAVISTA ALTA ABANCAY ABANCAY APURIMAC</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1237,7 +1237,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>8036</t>
+          <t>21952</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1262,27 +1262,27 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-13.63107169</t>
+          <t>-13.640022</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-72.88813747</t>
+          <t>-72.865096</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>POLICLINICO POLICIAL ABANCAY</t>
+          <t>AYMAS</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>JR. SANIDAD S/N BARRIO POLICIAL VILLA AMPAY NUMERO S/N DISTRITO ABANCAY PROVINCIA ABANCAY DEPARTAMENTO APURIMAC</t>
+          <t>CARRETERA BARRIO AYMAS  KM 1.5 CARRETERA ABANCAY-ATUMPATA NUMERO S/N DISTRITO ABANCAY PROVINCIA ABANCAY DEPARTAMENTO APURIMAC</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1299,7 +1299,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>7688</t>
+          <t>2663</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1324,27 +1324,27 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-13.6372697</t>
+          <t>-13.632941</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-72.8755924</t>
+          <t>-72.869839</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>CLINICA SANTA TERESA</t>
+          <t>VILLAGLORIA</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>AVENIDA AVENIDA ENRIQUE PELACH S/N S/N AVENIDA ENRIQUE PELACH S/N ABANCAY ABANCAY APURIMAC</t>
+          <t>PASAJE PASAJE LOS ANGELES S/N S/N PASAJE LOS ANGELES S/N ABANCAY ABANCAY APURIMAC</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>I-4</t>
+          <t>I-3</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1361,7 +1361,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>25996</t>
+          <t>7452</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1386,27 +1386,27 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-13.63485776</t>
+          <t>-13.6335283</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-72.8796795</t>
+          <t>-72.87692091</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD MENTAL COMUNITARIO "QHALI KAY"</t>
+          <t>METROPOLITANO</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>PASAJE SOUSA 118 1 COSTADO IZQUIERDO DEL HOTEL DE TURISTAS DE ABANCAY ABANCAY ABANCAY APURIMAC</t>
+          <t>JR. INCA GARCILAS0 DE LA VEGA Nº 250 JR. INCA GARCILAS0 DE LA VEGA Nº 250 ABANCAY ABANCAY APURIMAC</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>I-2</t>
+          <t>I-3</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1423,12 +1423,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>26572</t>
+          <t>8824</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>30104</t>
+          <t>30101</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1443,32 +1443,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CURAHUASI</t>
+          <t>ABANCAY</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-13.53785701</t>
+          <t>-13.65032955</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-72.69575002</t>
+          <t>-72.85170995</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD MENTAL COMUNITARIO "ALLIN KAWSAY"</t>
+          <t>ATUMPATA</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>AVENIDA LOS ROSALES NUMERO S/N PISO 1 DISTRITO CURAHUASI PROVINCIA ABANCAY DEPARTAMENTO APURIMAC</t>
+          <t>OTROS COMUNIDAD ATUMPATA S/N NUMERO S/N DISTRITO ABANCAY PROVINCIA ABANCAY DEPARTAMENTO APURIMAC</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1477,626 +1477,6 @@
         </is>
       </c>
       <c r="L17" t="inlineStr">
-        <is>
-          <t>030101</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>33277</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>30101</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>APURIMAC</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>ABANCAY</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>ABANCAY</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>-13.6401799</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>-72.8800236</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>CENTRO MEDIC PSICOMED JUAREZ</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>AVENIDA CIRCUNVALACION 1375 PISO 1 DISTRITO ABANCAY PROVINCIA ABANCAY DEPARTAMENTO APURIMAC</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>I-3</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>030101</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>34100</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>30101</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>APURIMAC</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>ABANCAY</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>ABANCAY</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>-13.6362788</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>-72.87988918</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>CONSULTORIO ESPECIALIZADO EN GINECOLOGIA Y OBSTETRICIA - CENTRO MUJER</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>AREQUIPA NUMERO 528 PISO 2 DISTRITO ABANCAY PROVINCIA ABANCAY DEPARTAMENTO APURIMAC</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>I-2</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>030101</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>26091</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>30101</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>APURIMAC</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>ABANCAY</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>ABANCAY</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>-13.63809542</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>-72.88655121</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>CENTRO MEDICO PSICOSOMATICO SEAOR DE LOS MILAGROS</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>URBANIZACION MZA. A LOTE. 10 URB. L.A. SANCHEZ (ESQ SINCHIROCA NUMERO 100 PISO 4 DISTRITO ABANCAY PROVINCIA ABANCAY DEPARTAMENTO APURIMAC</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>I-3</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>030101</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>32067</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>30101</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>APURIMAC</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>ABANCAY</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>ABANCAY</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>-13.6289407</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>-72.8848704</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>CENTRO OFTALMOLAGICO MONSEAOR ENRIQUE PELACH</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>URBANIZACION MAGISTERIAL URBANIZACION S/N DISTRITO ABANCAY PROVINCIA ABANCAY DEPARTAMENTO APURIMAC</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>I-3</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>030101</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>34549</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>30101</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>APURIMAC</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>ABANCAY</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>ABANCAY</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>-13.6335954</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>-72.8895222</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>CONSULTORIO DENTAL D' AGUILAR</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>PARAGUAY NUMERO 113 PISO 2 DISTRITO ABANCAY PROVINCIA ABANCAY DEPARTAMENTO APURIMAC</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>I-1</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>030101</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>36559</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>30101</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>APURIMAC</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>ABANCAY</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>ABANCAY</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>-13.63592187</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>-72.87788614</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>CONSULTORIO DENTAL SEAOR DE LOS MILAGROS</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>HUANCAVELICA NUMERO 304 PISO 2 INTERIOR 1 DISTRITO ABANCAY PROVINCIA ABANCAY DEPARTAMENTO APURIMAC</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>I-1</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>030101</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>28722</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>30101</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>APURIMAC</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>ABANCAY</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>ABANCAY</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>-13.63908878</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>-72.88021353</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>CENTRO MEDICO SERVI APURIMAC "C&amp;M" E.I.R.L</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>AVENIDA CENTENARIO NUMERO 143 PISO 1 INTERIOR 1 DISTRITO ABANCAY PROVINCIA ABANCAY DEPARTAMENTO APURIMAC</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>I-3</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>030101</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>32212</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>30101</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>APURIMAC</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>ABANCAY</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>ABANCAY</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>-13.6361173</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>-72.8829089</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>POLICLINICO TELLO E.I.R.L</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>LIMA NUMERO 866 DISTRITO ABANCAY PROVINCIA ABANCAY DEPARTAMENTO APURIMAC</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>I-3</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>030101</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>34454</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>30101</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>APURIMAC</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>ABANCAY</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>ABANCAY</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>-13.6352492</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>-72.8862318</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>CONSULTORIO DENTAL CARRASCO</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>AVENIDA CHILE 212 2 2 ESQUINA ENTRE LA  AV. CHILE Y LA AV. CANADA ABANCAY ABANCAY APURIMAC</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>I-1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>030101</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>34103</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>30101</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>APURIMAC</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>ABANCAY</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>ABANCAY</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>-13.6365915</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>-72.8791396</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>CONSULTORIO DENTAL ODONTO STETIC COLLAVINO</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>CUSCO NUMERO 218 PISO 2 DISTRITO ABANCAY PROVINCIA ABANCAY DEPARTAMENTO APURIMAC</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>I-1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
         <is>
           <t>030101</t>
         </is>

--- a/EstablecimientoSalud/excels/APURIMAC-ABANCAY-ABANCAY.xlsx
+++ b/EstablecimientoSalud/excels/APURIMAC-ABANCAY-ABANCAY.xlsx
@@ -425,35 +425,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ubigeo_gestor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PROVINCIA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DISTRITO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Codigo_Unico</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>UBIGEO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PROVINCIA</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DISTRITO</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LATITUD</t>
@@ -482,40 +482,35 @@
       <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Siniestros_fatales</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>ubigeo_gestor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>030101</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ABANCAY</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ABANCAY</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>11216</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>30104</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>APURIMAC</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>ABANCAY</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>CURAHUASI</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>-13.53678672</t>
@@ -544,40 +539,35 @@
       <c r="K2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>030101</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>030101</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ABANCAY</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ABANCAY</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>34572</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>30104</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>APURIMAC</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>ABANCAY</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>CURAHUASI</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>-13.537735</t>
@@ -606,40 +596,35 @@
       <c r="K3" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>030101</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>030101</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ABANCAY</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ABANCAY</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>8036</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>30101</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>APURIMAC</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>ABANCAY</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>ABANCAY</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>-13.63107169</t>
@@ -668,40 +653,35 @@
       <c r="K4" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>030101</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>030101</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ABANCAY</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ABANCAY</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>25996</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>30101</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>APURIMAC</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>ABANCAY</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>ABANCAY</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>-13.63485776</t>
@@ -730,40 +710,35 @@
       <c r="K5" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>030101</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>030101</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ABANCAY</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ABANCAY</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>26572</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>30104</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>APURIMAC</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>ABANCAY</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>CURAHUASI</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>-13.53785701</t>
@@ -792,40 +767,35 @@
       <c r="K6" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>030101</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>030101</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ABANCAY</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ABANCAY</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2661</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>30101</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>APURIMAC</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>ABANCAY</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>ABANCAY</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>-13.62778285</t>
@@ -854,40 +824,35 @@
       <c r="K7" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>030101</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>030101</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ABANCAY</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ABANCAY</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>11976</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>30101</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>APURIMAC</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>ABANCAY</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>ABANCAY</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>-13.64550167</t>
@@ -916,40 +881,35 @@
       <c r="K8" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>030101</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>030101</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ABANCAY</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ABANCAY</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2662</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>30101</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>APURIMAC</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>ABANCAY</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>ABANCAY</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>-13.6801621</t>
@@ -978,40 +938,35 @@
       <c r="K9" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>030101</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>030101</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ABANCAY</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ABANCAY</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>7689</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>30101</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>APURIMAC</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>ABANCAY</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>ABANCAY</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>-13.61922015</t>
@@ -1040,40 +995,35 @@
       <c r="K10" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>030101</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>030101</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ABANCAY</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ABANCAY</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>8828</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>30101</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>APURIMAC</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>ABANCAY</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>ABANCAY</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>-13.63810714</t>
@@ -1102,40 +1052,35 @@
       <c r="K11" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>030101</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>030101</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ABANCAY</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ABANCAY</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2659</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>30101</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>APURIMAC</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>ABANCAY</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>ABANCAY</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>-13.62899</t>
@@ -1164,40 +1109,35 @@
       <c r="K12" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>030101</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>030101</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ABANCAY</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ABANCAY</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2664</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>30101</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>APURIMAC</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>ABANCAY</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>ABANCAY</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>-13.63543084</t>
@@ -1226,40 +1166,35 @@
       <c r="K13" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>030101</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>030101</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ABANCAY</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ABANCAY</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>21952</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>30101</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>APURIMAC</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>ABANCAY</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>ABANCAY</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>-13.640022</t>
@@ -1288,40 +1223,35 @@
       <c r="K14" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>030101</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>030101</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ABANCAY</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ABANCAY</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>2663</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>30101</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>APURIMAC</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>ABANCAY</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>ABANCAY</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>-13.632941</t>
@@ -1350,40 +1280,35 @@
       <c r="K15" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>030101</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>030101</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ABANCAY</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ABANCAY</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>7452</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>30101</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>APURIMAC</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>ABANCAY</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>ABANCAY</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>-13.6335283</t>
@@ -1412,40 +1337,35 @@
       <c r="K16" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>030101</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>030101</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ABANCAY</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ABANCAY</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>8824</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>30101</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>APURIMAC</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>ABANCAY</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>ABANCAY</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>-13.65032955</t>
@@ -1474,11 +1394,6 @@
       <c r="K17" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>030101</t>
         </is>
       </c>
     </row>

--- a/EstablecimientoSalud/excels/APURIMAC-ABANCAY-ABANCAY.xlsx
+++ b/EstablecimientoSalud/excels/APURIMAC-ABANCAY-ABANCAY.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Codigo_Unico</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
